--- a/empirical_study/DisambiguationGuide.xlsx
+++ b/empirical_study/DisambiguationGuide.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="68">
   <si>
     <t>Disambiguation matrix for symptoms</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Original category \ confused category</t>
   </si>
   <si>
-    <t>Long Execution Time for Kernel Function</t>
-  </si>
-  <si>
-    <t>Long Execution Time for Code Blocks</t>
+    <t>Long Kernel Execution Time</t>
   </si>
   <si>
     <t>Long Kernel Launch Time</t>
@@ -67,15 +64,9 @@
     <t>-</t>
   </si>
   <si>
-    <t>The post only mentioned that the overall kernel execution time is long.</t>
-  </si>
-  <si>
     <t>The two occur at different steps of CUDA program execution. This category refers to long duration in the Kernel Execution step.</t>
   </si>
   <si>
-    <t>The post mentioned that specific code blocks have a long execution time.</t>
-  </si>
-  <si>
     <t>The two occur at different steps of CUDA program execution. This category refers to long duration in the Kernel Launch step.</t>
   </si>
   <si>
@@ -121,6 +112,12 @@
     <t>Imbalanced Thread Workload</t>
   </si>
   <si>
+    <t>Focuses on whether memory access can be coalesced, rather than whether the memory access is redundant.</t>
+  </si>
+  <si>
+    <t>The process occurs during memory access, rather than memory allocation.</t>
+  </si>
+  <si>
     <t>Inefficient Loop Unrolling</t>
   </si>
   <si>
@@ -160,33 +157,27 @@
     <t>Unable to Perform Automatic Inlining Optimization</t>
   </si>
   <si>
-    <t>Focuses on whether memory access can be coalesced, rather than whether the memory access is redundant.</t>
-  </si>
-  <si>
-    <t>The process occurs during memory access, rather than memory allocation.</t>
-  </si>
-  <si>
     <t>The cause lies in the mismatch between the memory type used and the access pattern, not necessarily limited to shared memory.</t>
   </si>
   <si>
+    <t>This category focuses on redundant memory accesses, rather than whether the memory addresses are contiguous.</t>
+  </si>
+  <si>
     <t>Focuses on the memory type, rather than the data type.</t>
   </si>
   <si>
-    <t>This category focuses on redundant memory accesses, rather than whether the memory addresses are contiguous.</t>
+    <t>The process occurs during memory allocation, rather than memory access.</t>
   </si>
   <si>
     <t>The redundancy refers to memory access, not synchronization.</t>
   </si>
   <si>
-    <t>The process occurs during memory allocation, rather than memory access.</t>
+    <t>Bank conflicts occur only in shared memory and are not related to other memory types.</t>
   </si>
   <si>
     <t>Occurs during the memory allocation process, not the data transfer process.</t>
   </si>
   <si>
-    <t>Bank conflicts occur only in shared memory and are not related to other memory types.</t>
-  </si>
-  <si>
     <t>The cause lies in the cache, not the memory.</t>
   </si>
   <si>
@@ -199,10 +190,13 @@
     <t>Focuses on loop statements and is related to loop control overhead.</t>
   </si>
   <si>
+    <t>The redundancy refers to synchronization, not memory access.</t>
+  </si>
+  <si>
     <t>Focuses on branch statements and considers threads in the same warp taking different execution paths.</t>
   </si>
   <si>
-    <t>The redundancy refers to synchronization, not memory access.</t>
+    <t>Focuses on the data type, rather than the memory type.</t>
   </si>
   <si>
     <t>The existing API is used, but it is used incorrectly or an API unsuitable for the given workload is selected.</t>
@@ -211,16 +205,13 @@
     <t>It is a performance problem in the developer's use of the API, and the API provided by the CUDA Toolkits is not problematic.</t>
   </si>
   <si>
-    <t>Focuses on the data type, rather than the memory type.</t>
-  </si>
-  <si>
     <t>Occurs during the data transfer process, not the memory allocation process.</t>
   </si>
   <si>
+    <t>Focuses on whether the algorithm itself is efficient, rather than the workload of each thread.</t>
+  </si>
+  <si>
     <t>The selected algorithm itself is inefficient.</t>
-  </si>
-  <si>
-    <t>Focuses on whether the algorithm itself is efficient, rather than the workload of each thread.</t>
   </si>
   <si>
     <t>The algorithm is efficient in serial execution but does not adapt well to the characteristics of GPU hardware.</t>
@@ -963,7 +954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1001,15 +992,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1340,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1365,1826 +1347,1777 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:1">
+      <c r="A13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:23">
-      <c r="A14" s="2" t="s">
-        <v>0</v>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="W14" s="12"/>
     </row>
     <row r="15" spans="1:23">
-      <c r="A15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="A15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="F15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="L15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="N15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="O15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="R15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="T15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="U15" s="4" t="s">
+      <c r="V15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="V15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="W15" s="13"/>
+      <c r="W15" s="12"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W16" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W16" s="13"/>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W17" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W17" s="13"/>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W18" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W18" s="13"/>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W19" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W19" s="13"/>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W20" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W20" s="13"/>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W21" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W21" s="13"/>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W22" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W22" s="13"/>
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W23" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W23" s="13"/>
     </row>
     <row r="24" spans="1:23">
       <c r="A24" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W24" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W24" s="13"/>
     </row>
     <row r="25" spans="1:23">
       <c r="A25" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W25" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W25" s="13"/>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W26" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W26" s="13"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W27" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W27" s="13"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W28" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W28" s="13"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W29" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W29" s="13"/>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W30" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W30" s="13"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W31" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W31" s="13"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W32" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W32" s="13"/>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W33" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="W33" s="13"/>
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="V34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="W34" s="13"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="T35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="U35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="V35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W35" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="V34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W34" s="14"/>
-    </row>
-    <row r="35" spans="1:23">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="N35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="P35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="R35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="S35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="T35" s="6" t="s">
+    </row>
+    <row r="36" spans="2:23">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="S36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="T36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="U35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="V35" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="W35" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="O36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="T36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="V36" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="W36" s="15"/>
+        <v>10</v>
+      </c>
+      <c r="W36" s="13"/>
     </row>
     <row r="37" spans="2:23">
       <c r="B37" s="6"/>
@@ -3208,7 +3141,7 @@
       <c r="T37" s="6"/>
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
-      <c r="W37" s="16"/>
+      <c r="W37" s="13"/>
     </row>
     <row r="38" spans="2:23">
       <c r="B38" s="6"/>
@@ -3232,7 +3165,7 @@
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
-      <c r="W38" s="16"/>
+      <c r="W38" s="13"/>
     </row>
     <row r="39" spans="2:23">
       <c r="B39" s="6"/>
@@ -3522,15 +3455,7 @@
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
     </row>
-    <row r="51" spans="2:23">
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
+    <row r="51" spans="10:23">
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
